--- a/график.xlsx
+++ b/график.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sssab\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8b23f244c3943c43/Документы/GitHub/parallel_prog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3572C203-7BE9-4EC8-8834-ED27AD66B4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3572C203-7BE9-4EC8-8834-ED27AD66B4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6383922D-DADF-4CE7-B934-BCD273943EE5}"/>
   <bookViews>
-    <workbookView xWindow="348" yWindow="648" windowWidth="12936" windowHeight="11244" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1836" yWindow="1476" windowWidth="12936" windowHeight="11244" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,16 +30,16 @@
     <t>размер</t>
   </si>
   <si>
-    <t>1 поток</t>
+    <t>1 процесс</t>
   </si>
   <si>
-    <t>2 потока</t>
+    <t>2 процесса</t>
   </si>
   <si>
-    <t>4 потока</t>
+    <t>4 процесса</t>
   </si>
   <si>
-    <t>8 потоков</t>
+    <t>8 процессов</t>
   </si>
 </sst>
 </file>
@@ -201,7 +201,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1 поток</c:v>
+                  <c:v>1 процесс</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -288,7 +288,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2 потока</c:v>
+                  <c:v>2 процесса</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -375,7 +375,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4 потока</c:v>
+                  <c:v>4 процесса</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -462,7 +462,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>8 потоков</c:v>
+                  <c:v>8 процессов</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
